--- a/output/employee_data_clean.xlsx
+++ b/output/employee_data_clean.xlsx
@@ -516,12 +516,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2002-07-11</t>
+          <t>2002/07/11</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2017-02-03</t>
+          <t>2017/02/03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021/09/16</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -591,12 +591,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1980-12-21</t>
+          <t>1980/12/21</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2016-12-19</t>
+          <t>2016/12/19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1989-10-08</t>
+          <t>1989/10/08</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2020/05/03</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2020-01-04</t>
+          <t>2020/01/04</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1977-10-18</t>
+          <t>1977/10/18</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025/01/18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1984-05-09</t>
+          <t>1984/05/09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023/05/22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -873,12 +873,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1980-05-10</t>
+          <t>1980/05/10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2016-11-30</t>
+          <t>2016/11/30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2021-10-03</t>
+          <t>2021/10/03</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -944,12 +944,12 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1991-09-16</t>
+          <t>1991/09/16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020/09/10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025/05/16</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1980-10-07</t>
+          <t>1980/10/07</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2018-02-03</t>
+          <t>2018/02/03</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2023-07-23</t>
+          <t>2023/07/23</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1976-07-01</t>
+          <t>1976/07/01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2023/09/15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1995-03-10</t>
+          <t>1995/03/10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2023/11/15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026/03/04</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1984-08-09</t>
+          <t>1984/08/09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2021-07-15</t>
+          <t>2021/07/15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2022-11-27</t>
+          <t>2022/11/27</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1316,7 +1316,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2017-05-18</t>
+          <t>2017/05/18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2018-06-11</t>
+          <t>2018/06/11</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1982-01-03</t>
+          <t>1982/01/03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2024/01/14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2027-08-28</t>
+          <t>2027/08/28</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2004-10-28</t>
+          <t>2004/10/28</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2015-06-29</t>
+          <t>2015/06/29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1980-04-03</t>
+          <t>1980/04/03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2016-08-09</t>
+          <t>2016/08/09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1991-11-08</t>
+          <t>1991/11/08</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2023-03-12</t>
+          <t>2023/03/12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1985-05-11</t>
+          <t>1985/05/11</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2016-05-26</t>
+          <t>2016/05/26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
+          <t>2022/02/10</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1749,12 +1749,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1978-03-25</t>
+          <t>1978/03/25</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024/05/21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2023/12/31</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1820,12 +1820,12 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2000-06-03</t>
+          <t>2000/06/03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2020-03-02</t>
+          <t>2020/03/02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2021-10-24</t>
+          <t>2021/10/24</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1980-08-20</t>
+          <t>1980/08/20</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2015-03-02</t>
+          <t>2015/03/02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1933,7 +1933,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2019-03-15</t>
+          <t>2019/03/15</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1976-06-07</t>
+          <t>1976/06/07</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025/05/18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2002-06-23</t>
+          <t>2002/06/23</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2024-03-06</t>
+          <t>2024/03/06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1981-10-15</t>
+          <t>1981/10/15</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2015-11-12</t>
+          <t>2015/11/12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1981-12-15</t>
+          <t>1981/12/15</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2015-03-10</t>
+          <t>2015/03/10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2016-10-15</t>
+          <t>2016/10/15</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1978-09-22</t>
+          <t>1978/09/22</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2019-09-04</t>
+          <t>2019/09/04</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1984-06-13</t>
+          <t>1984/06/13</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2024-10-14</t>
+          <t>2024/10/14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2030-06-20</t>
+          <t>2030/06/20</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1977-10-06</t>
+          <t>1977/10/06</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2018-06-17</t>
+          <t>2018/06/17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2019/10/31</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2467,12 +2467,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1997-07-13</t>
+          <t>1997/07/13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2019-12-24</t>
+          <t>2019/12/24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2022/10/07</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1986-10-12</t>
+          <t>1986/10/12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2015-04-15</t>
+          <t>2015/04/15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1992-09-15</t>
+          <t>1992/09/15</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2018-08-11</t>
+          <t>2018/08/11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1987-08-08</t>
+          <t>1987/08/08</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2018-01-07</t>
+          <t>2018/01/07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1992-12-13</t>
+          <t>1992/12/13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2018-10-30</t>
+          <t>2018/10/30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2822,12 +2822,12 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1998-04-03</t>
+          <t>1998/04/03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2017-03-04</t>
+          <t>2017/03/04</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2894,7 +2894,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2021/03/12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025/02/23</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1990-07-01</t>
+          <t>1990/07/01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2015-03-14</t>
+          <t>2015/03/14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1980-03-06</t>
+          <t>1980/03/06</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2018-08-25</t>
+          <t>2018/08/25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2019-06-21</t>
+          <t>2019/06/21</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1998-02-22</t>
+          <t>1998/02/22</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2015-04-14</t>
+          <t>2015/04/14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023/06/05</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1977-11-25</t>
+          <t>1977/11/25</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2015-06-03</t>
+          <t>2015/06/03</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1982-02-25</t>
+          <t>1982/02/25</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2016-03-09</t>
+          <t>2016/03/09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3322,7 +3322,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>2020/10/26</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3386,12 +3386,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1988-04-08</t>
+          <t>1988/04/08</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2022/05/15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2001-01-09</t>
+          <t>2001/01/09</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2023/01/31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024/04/17</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3532,12 +3532,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2002-06-10</t>
+          <t>2002/06/10</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2017-11-25</t>
+          <t>2017/11/25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1990-08-12</t>
+          <t>1990/08/12</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2018/04/26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2017-05-16</t>
+          <t>2017/05/16</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1977-06-13</t>
+          <t>1977/06/13</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024/11/06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2027-01-12</t>
+          <t>2027/01/12</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1993-06-27</t>
+          <t>1993/06/27</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2015-01-18</t>
+          <t>2015/01/18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1983-09-12</t>
+          <t>1983/09/12</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2015-04-21</t>
+          <t>2015/04/21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1989-10-06</t>
+          <t>1989/10/06</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2015-06-18</t>
+          <t>2015/06/18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2019-11-05</t>
+          <t>2019/11/05</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1991-04-05</t>
+          <t>1991/04/05</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2020-02-27</t>
+          <t>2020/02/27</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026/09/13</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1991-03-03</t>
+          <t>1991/03/03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
+          <t>2022/08/17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1990-08-20</t>
+          <t>1990/08/20</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
+          <t>2020/10/24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1978-06-24</t>
+          <t>1978/06/24</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2020-03-05</t>
+          <t>2020/03/05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2022-01-01</t>
+          <t>2022/01/01</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -4246,12 +4246,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1994-11-23</t>
+          <t>1994/11/23</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2024-12-21</t>
+          <t>2024/12/21</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1984-10-24</t>
+          <t>1984/10/24</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2017-11-17</t>
+          <t>2017/11/17</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025/03/05</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1986-08-16</t>
+          <t>1986/08/16</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025/03/15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1977-03-12</t>
+          <t>1977/03/12</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2017-08-21</t>
+          <t>2017/08/21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2020-03-13</t>
+          <t>2020/03/13</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1987-09-09</t>
+          <t>1987/09/09</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2023/08/13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2029-09-23</t>
+          <t>2029/09/23</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1975-11-13</t>
+          <t>1975/11/13</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2021-08-21</t>
+          <t>2021/08/21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026/08/19</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1979-07-11</t>
+          <t>1979/07/11</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024/05/10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2027-06-06</t>
+          <t>2027/06/06</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2001-08-20</t>
+          <t>2001/08/20</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2021-02-11</t>
+          <t>2021/02/11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1976-01-01</t>
+          <t>1976/01/01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2017-04-23</t>
+          <t>2017/04/23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2021/09/30</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1998-04-28</t>
+          <t>1998/04/28</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2019-10-24</t>
+          <t>2019/10/24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024/04/23</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1987-09-28</t>
+          <t>1987/09/28</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
+          <t>2017/02/13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021/09/26</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5048,7 +5048,7 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
+          <t>2019/03/11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1995-05-15</t>
+          <t>1995/05/15</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2015-05-19</t>
+          <t>2015/05/19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1985-01-16</t>
+          <t>1985/01/16</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2024/12/13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2031-05-17</t>
+          <t>2031/05/17</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1996-07-22</t>
+          <t>1996/07/22</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2016-05-19</t>
+          <t>2016/05/19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2017-07-08</t>
+          <t>2017/07/08</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1978-04-05</t>
+          <t>1978/04/05</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2020-04-22</t>
+          <t>2020/04/22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026/02/07</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1996-04-13</t>
+          <t>1996/04/13</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2023-01-25</t>
+          <t>2023/01/25</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1991-03-19</t>
+          <t>1991/03/19</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2017-09-11</t>
+          <t>2017/09/11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1995-01-28</t>
+          <t>1995/01/28</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2020-07-30</t>
+          <t>2020/07/30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1975-09-27</t>
+          <t>1975/09/27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
+          <t>2022/09/09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2027-04-10</t>
+          <t>2027/04/10</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -5694,12 +5694,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1994-01-01</t>
+          <t>1994/01/01</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025/02/11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1996-07-16</t>
+          <t>1996/07/16</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2015/10/28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5836,12 +5836,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1978-12-24</t>
+          <t>1978/12/24</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2017-05-05</t>
+          <t>2017/05/05</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1986-04-09</t>
+          <t>1986/04/09</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
+          <t>2023/12/02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1984-10-21</t>
+          <t>1984/10/21</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2020-10-14</t>
+          <t>2020/10/14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2020-07-20</t>
+          <t>2020/07/20</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2015-05-05</t>
+          <t>2015/05/05</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2020-11-15</t>
+          <t>2020/11/15</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6124,12 +6124,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1989/01/01</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024/09/06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2030-10-09</t>
+          <t>2030/10/09</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2001-08-19</t>
+          <t>2001/08/19</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023/06/27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1994-04-23</t>
+          <t>1994/04/23</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2017-11-12</t>
+          <t>2017/11/12</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024/02/01</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1994-05-01</t>
+          <t>1994/05/01</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
+          <t>2023/09/01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2029-02-21</t>
+          <t>2029/02/21</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -6416,12 +6416,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1997-12-26</t>
+          <t>1997/12/26</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2019-12-25</t>
+          <t>2019/12/25</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2021-10-23</t>
+          <t>2021/10/23</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6487,12 +6487,12 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1983-02-17</t>
+          <t>1983/02/17</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021/10/29</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1990-05-11</t>
+          <t>1990/05/11</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2017-03-23</t>
+          <t>2017/03/23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
+          <t>2021/05/12</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6625,12 +6625,12 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1988-05-20</t>
+          <t>1988/05/20</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2017-09-29</t>
+          <t>2017/09/29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6694,12 +6694,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1985-07-09</t>
+          <t>1985/07/09</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2016-01-22</t>
+          <t>2016/01/22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022/10/26</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1994-11-06</t>
+          <t>1994/11/06</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2015-02-25</t>
+          <t>2015/02/25</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1986-09-05</t>
+          <t>1986/09/05</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2015/08/12</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2002-07-12</t>
+          <t>2002/07/12</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2016-12-03</t>
+          <t>2016/12/03</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2020-03-21</t>
+          <t>2020/03/21</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6986,12 +6986,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1987-03-08</t>
+          <t>1987/03/08</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2016-09-11</t>
+          <t>2016/09/11</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2016-05-23</t>
+          <t>2016/05/23</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>1982-09-23</t>
+          <t>1982/09/23</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2020-01-16</t>
+          <t>2020/01/16</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026/02/18</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1989-02-08</t>
+          <t>1989/02/08</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2021-01-10</t>
+          <t>2021/01/10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1983-12-24</t>
+          <t>1983/12/24</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018/08/28</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1998-01-08</t>
+          <t>1998/01/08</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2020-02-07</t>
+          <t>2020/02/07</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024/07/02</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2000-08-02</t>
+          <t>2000/08/02</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2018-11-18</t>
+          <t>2018/11/18</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2018/06/23</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2004-12-28</t>
+          <t>2004/12/28</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2016-07-09</t>
+          <t>2016/07/09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>1981-10-14</t>
+          <t>1981/10/14</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2016-04-01</t>
+          <t>2016/04/01</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023/08/15</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>1999-06-07</t>
+          <t>1999/06/07</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>2022/02/09</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2002-09-14</t>
+          <t>2002/09/14</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2020-05-17</t>
+          <t>2020/05/17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1996-10-09</t>
+          <t>1996/10/09</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2021-09-16</t>
+          <t>2021/09/16</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2022/10/08</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7781,12 +7781,12 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>1981-09-08</t>
+          <t>1981/09/08</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2022-02-02</t>
+          <t>2022/02/02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
+          <t>2021/08/22</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7852,12 +7852,12 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>1984-08-26</t>
+          <t>1984/08/26</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2015-06-11</t>
+          <t>2015/06/11</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2017/10/06</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7927,12 +7927,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>1979-12-07</t>
+          <t>1979/12/07</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2020-08-02</t>
+          <t>2020/08/02</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2023-07-02</t>
+          <t>2023/07/02</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1976-08-28</t>
+          <t>1976/08/28</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2021-11-02</t>
+          <t>2021/11/02</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2029-04-23</t>
+          <t>2029/04/23</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -8073,12 +8073,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>1983-11-17</t>
+          <t>1983/11/17</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024/10/07</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2001-11-28</t>
+          <t>2001/11/28</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2022/07/22</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2000-01-19</t>
+          <t>2000/01/19</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2023-06-06</t>
+          <t>2023/06/06</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>2027-09-01</t>
+          <t>2027/09/01</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2002-05-20</t>
+          <t>2002/05/20</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2018-04-05</t>
+          <t>2018/04/05</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2019-11-06</t>
+          <t>2019/11/06</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8357,12 +8357,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>1995-04-13</t>
+          <t>1995/04/13</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
+          <t>2019/09/08</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>2019-02-24</t>
+          <t>2019/02/24</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>1977-06-14</t>
+          <t>1977/06/14</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2025/04/03</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2032-09-13</t>
+          <t>2032/09/13</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2004-12-24</t>
+          <t>2004/12/24</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2016-02-25</t>
+          <t>2016/02/25</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2017-07-09</t>
+          <t>2017/07/09</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1997-03-25</t>
+          <t>1997/03/25</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2018-10-24</t>
+          <t>2018/10/24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025/08/23</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1981-12-24</t>
+          <t>1981/12/24</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2023-07-09</t>
+          <t>2023/07/09</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1993-10-21</t>
+          <t>1993/10/21</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2019-04-17</t>
+          <t>2019/04/17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>1991-11-28</t>
+          <t>1991/11/28</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2017-09-12</t>
+          <t>2017/09/12</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2019-08-09</t>
+          <t>2019/08/09</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1977-10-04</t>
+          <t>1977/10/04</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2016-12-09</t>
+          <t>2016/12/09</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2018-03-12</t>
+          <t>2018/03/12</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8943,12 +8943,12 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1983-01-25</t>
+          <t>1983/01/25</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2015-09-10</t>
+          <t>2015/09/10</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2015-05-26</t>
+          <t>2015/05/26</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1985-10-16</t>
+          <t>1985/10/16</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2019-11-15</t>
+          <t>2019/11/15</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2022-06-14</t>
+          <t>2022/06/14</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1983-02-02</t>
+          <t>1983/02/02</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2017-05-31</t>
+          <t>2017/05/31</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2018/10/13</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2002-05-03</t>
+          <t>2002/05/03</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
+          <t>2021/12/15</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1991-10-10</t>
+          <t>1991/10/10</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2016-01-13</t>
+          <t>2016/01/13</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2015-07-18</t>
+          <t>2015/07/18</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9312,12 +9312,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1980-01-12</t>
+          <t>1980/01/12</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024/06/20</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9383,12 +9383,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1989-12-03</t>
+          <t>1989/12/03</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2019-02-15</t>
+          <t>2019/02/15</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2020-06-29</t>
+          <t>2020/06/29</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9450,12 +9450,12 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>1991-06-24</t>
+          <t>1991/06/24</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2018-08-23</t>
+          <t>2018/08/23</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>1987-07-16</t>
+          <t>1987/07/16</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2023/02/09</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2028-01-29</t>
+          <t>2028/01/29</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>1990-07-07</t>
+          <t>1990/07/07</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023/12/10</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2030-06-25</t>
+          <t>2030/06/25</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9667,12 +9667,12 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2000-05-03</t>
+          <t>2000/05/03</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2017-01-20</t>
+          <t>2017/01/20</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2002-11-25</t>
+          <t>2002/11/25</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
+          <t>2021/08/22</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2024-01-08</t>
+          <t>2024/01/08</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9809,12 +9809,12 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>1976-03-21</t>
+          <t>1976/03/21</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
+          <t>2021/05/17</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>1977-02-26</t>
+          <t>1977/02/26</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2015-12-01</t>
+          <t>2015/12/01</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9916,7 +9916,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
+          <t>2023/01/13</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9954,7 +9954,7 @@
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2021-07-11</t>
+          <t>2021/07/11</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024/06/17</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>1980-04-23</t>
+          <t>1980/04/23</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2016/08/24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10091,12 +10091,12 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>1991-11-22</t>
+          <t>1991/11/22</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2022-01-22</t>
+          <t>2022/01/22</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>2022/10/29</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
@@ -10160,12 +10160,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>1986-04-24</t>
+          <t>1986/04/24</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023/10/31</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10231,12 +10231,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>1989-02-24</t>
+          <t>1989/02/24</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2019-01-31</t>
+          <t>2019/01/31</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>1980-10-27</t>
+          <t>1980/10/27</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2017-03-22</t>
+          <t>2017/03/22</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2021-04-03</t>
+          <t>2021/04/03</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>1979-08-04</t>
+          <t>1979/08/04</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024/06/25</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2032-06-11</t>
+          <t>2032/06/11</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10450,12 +10450,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>1985-11-07</t>
+          <t>1985/11/07</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022/10/19</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025/04/13</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10525,12 +10525,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2000-12-28</t>
+          <t>2000/12/28</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025/03/20</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2029-07-26</t>
+          <t>2029/07/26</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>1976-03-15</t>
+          <t>1976/03/15</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2018-09-27</t>
+          <t>2018/09/27</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10671,12 +10671,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>1993-03-10</t>
+          <t>1993/03/10</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2016-05-17</t>
+          <t>2016/05/17</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2021-03-28</t>
+          <t>2021/03/28</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>1981-05-22</t>
+          <t>1981/05/22</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2020-10-01</t>
+          <t>2020/10/01</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>2028-03-10</t>
+          <t>2028/03/10</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>1997-08-13</t>
+          <t>1997/08/13</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2015-12-30</t>
+          <t>2015/12/30</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2023-06-21</t>
+          <t>2023/06/21</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10892,12 +10892,12 @@
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>1975-09-21</t>
+          <t>1975/09/21</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2016-03-09</t>
+          <t>2016/03/09</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10959,12 +10959,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>1979-11-28</t>
+          <t>1979/11/28</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2019-11-29</t>
+          <t>2019/11/29</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025/04/15</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11034,12 +11034,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>1993-07-03</t>
+          <t>1993/07/03</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024/12/14</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>2031-12-06</t>
+          <t>2031/12/06</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11109,12 +11109,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>1980-06-11</t>
+          <t>1980/06/11</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2019/09/22</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026/03/20</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11184,12 +11184,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>1981-09-03</t>
+          <t>1981/09/03</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2018-04-15</t>
+          <t>2018/04/15</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11247,12 +11247,12 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>1978-03-16</t>
+          <t>1978/03/16</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024/05/20</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>1984-09-16</t>
+          <t>1984/09/16</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2017-11-26</t>
+          <t>2017/11/26</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025/06/13</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11391,12 +11391,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2001-09-10</t>
+          <t>2001/09/10</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2016-01-21</t>
+          <t>2016/01/21</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2004-08-17</t>
+          <t>2004/08/17</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2019-02-12</t>
+          <t>2019/02/12</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11529,12 +11529,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>1980-04-08</t>
+          <t>1980/04/08</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2016-08-04</t>
+          <t>2016/08/04</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11600,12 +11600,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>1985-12-04</t>
+          <t>1985/12/04</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
+          <t>2019/05/22</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>1986-07-04</t>
+          <t>1986/07/04</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2018-01-02</t>
+          <t>2018/01/02</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2020/05/15</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>1998-02-23</t>
+          <t>1998/02/23</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2020/09/29</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11818,7 +11818,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2022-01-29</t>
+          <t>2022/01/29</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2002-06-04</t>
+          <t>2002/06/04</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2017-08-22</t>
+          <t>2017/08/22</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>1994-10-03</t>
+          <t>1994/10/03</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2020-03-01</t>
+          <t>2020/03/01</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12024,12 +12024,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>1992-01-14</t>
+          <t>1992/01/14</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2019-05-26</t>
+          <t>2019/05/26</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-12-24</t>
+          <t>2026/12/24</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1977-08-27</t>
+          <t>1977/08/27</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024/09/09</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025/06/09</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>1979-06-02</t>
+          <t>1979/06/02</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2015-10-01</t>
+          <t>2015/10/01</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
+          <t>2017/06/27</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12249,12 +12249,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2002-04-17</t>
+          <t>2002/04/17</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2023/10/22</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12320,12 +12320,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>1994-09-03</t>
+          <t>1994/09/03</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2019-05-27</t>
+          <t>2019/05/27</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2024-05-11</t>
+          <t>2024/05/11</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>1986-02-16</t>
+          <t>1986/02/16</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2017-06-10</t>
+          <t>2017/06/10</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>1978-04-08</t>
+          <t>1978/04/08</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2015-09-25</t>
+          <t>2015/09/25</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2002-12-25</t>
+          <t>2002/12/25</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025/05/17</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2030-04-01</t>
+          <t>2030/04/01</t>
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1991-01-21</t>
+          <t>1991/01/21</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2019-11-26</t>
+          <t>2019/11/26</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2020-12-06</t>
+          <t>2020/12/06</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12679,12 +12679,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1989-11-05</t>
+          <t>1989/11/05</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2023-02-16</t>
+          <t>2023/02/16</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1986-12-08</t>
+          <t>1986/12/08</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2016-09-03</t>
+          <t>2016/09/03</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2001-03-12</t>
+          <t>2001/03/12</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2023/09/16</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2031-06-16</t>
+          <t>2031/06/16</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12896,12 +12896,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1997-09-24</t>
+          <t>1997/09/24</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024/03/21</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>1995-05-21</t>
+          <t>1995/05/21</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
+          <t>2020/06/25</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13003,7 +13003,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2021-02-14</t>
+          <t>2021/02/14</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13040,12 +13040,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>1982-02-02</t>
+          <t>1982/02/02</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2015-01-19</t>
+          <t>2015/01/19</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2019-10-16</t>
+          <t>2019/10/16</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13115,12 +13115,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>1992-10-28</t>
+          <t>1992/10/28</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2016-10-21</t>
+          <t>2016/10/21</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>1997-07-17</t>
+          <t>1997/07/17</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2021-01-03</t>
+          <t>2021/01/03</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
+          <t>2022/05/31</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>1990-09-22</t>
+          <t>1990/09/22</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
+          <t>2018/11/08</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023/12/15</t>
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
@@ -13332,12 +13332,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>1994-05-19</t>
+          <t>1994/05/19</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2023-12-29</t>
+          <t>2023/12/29</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13403,12 +13403,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>1983-04-26</t>
+          <t>1983/04/26</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2015-08-05</t>
+          <t>2015/08/05</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2004-10-26</t>
+          <t>2004/10/26</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
+          <t>2020/01/02</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2004-03-19</t>
+          <t>2004/03/19</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2017-09-27</t>
+          <t>2017/09/27</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
+          <t>2019/06/23</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13616,12 +13616,12 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1975-03-19</t>
+          <t>1975/03/19</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2022/10/30</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13687,12 +13687,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>1975-05-09</t>
+          <t>1975/05/09</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2022-12-17</t>
+          <t>2022/12/17</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>1985-01-03</t>
+          <t>1985/01/03</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2022-01-10</t>
+          <t>2022/01/10</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13829,12 +13829,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>1975-09-28</t>
+          <t>1975/09/28</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2021-03-08</t>
+          <t>2021/03/08</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>1978-07-16</t>
+          <t>1978/07/16</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2016-12-04</t>
+          <t>2016/12/04</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2001-08-05</t>
+          <t>2001/08/05</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
+          <t>2022/07/06</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14040,12 +14040,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>1989-09-04</t>
+          <t>1989/09/04</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2016-12-12</t>
+          <t>2016/12/12</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2021-07-23</t>
+          <t>2021/07/23</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14115,12 +14115,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2000-03-05</t>
+          <t>2000/03/05</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2016-11-08</t>
+          <t>2016/11/08</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2019-01-03</t>
+          <t>2019/01/03</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14190,12 +14190,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004/08/01</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2020-03-23</t>
+          <t>2020/03/23</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2023/01/03</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14265,12 +14265,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>1986-11-04</t>
+          <t>1986/11/04</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2017-03-21</t>
+          <t>2017/03/21</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14336,12 +14336,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>1997-01-28</t>
+          <t>1997/01/28</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025/05/03</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>2031-02-24</t>
+          <t>2031/02/24</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14407,12 +14407,12 @@
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2001-05-11</t>
+          <t>2001/05/11</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2016/08/15</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14445,7 +14445,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2015-10-18</t>
+          <t>2015/10/18</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14482,12 +14482,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1981-09-18</t>
+          <t>1981/09/18</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2024/12/31</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025/11/22</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14557,12 +14557,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1979-06-08</t>
+          <t>1979/06/08</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2019-11-25</t>
+          <t>2019/11/25</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2004-05-23</t>
+          <t>2004/05/23</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024/01/06</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>1996-02-10</t>
+          <t>1996/02/10</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2023/01/28</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14770,12 +14770,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>1981-11-10</t>
+          <t>1981/11/10</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2016-05-13</t>
+          <t>2016/05/13</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14841,12 +14841,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2003-09-26</t>
+          <t>2003/09/26</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2019-07-07</t>
+          <t>2019/07/07</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -14912,12 +14912,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>1980-04-04</t>
+          <t>1980/04/04</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2020-10-11</t>
+          <t>2020/10/11</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -14950,7 +14950,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2023/05/09</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14987,12 +14987,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>1989-12-08</t>
+          <t>1989/12/08</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2017-03-31</t>
+          <t>2017/03/31</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15054,12 +15054,12 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>1998-06-15</t>
+          <t>1998/06/15</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2017-09-12</t>
+          <t>2017/09/12</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>1995-07-25</t>
+          <t>1995/07/25</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2017-01-31</t>
+          <t>2017/01/31</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2021-07-12</t>
+          <t>2021/07/12</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15192,12 +15192,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>1990-03-24</t>
+          <t>1990/03/24</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2017-07-21</t>
+          <t>2017/07/21</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -15263,12 +15263,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>1997-12-11</t>
+          <t>1997/12/11</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2019-01-26</t>
+          <t>2019/01/26</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>1976-11-28</t>
+          <t>1976/11/28</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2025-01-15</t>
+          <t>2025/01/15</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -15405,12 +15405,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>1998-01-05</t>
+          <t>1998/01/05</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
+          <t>2019/06/25</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15443,7 +15443,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2027-04-18</t>
+          <t>2027/04/18</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15480,12 +15480,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2002-04-03</t>
+          <t>2002/04/03</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
+          <t>2024/03/11</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2029-04-28</t>
+          <t>2029/04/28</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15551,12 +15551,12 @@
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>1988-09-11</t>
+          <t>1988/09/11</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2015-07-31</t>
+          <t>2015/07/31</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -15622,12 +15622,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>1976-01-09</t>
+          <t>1976/01/09</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2020-03-03</t>
+          <t>2020/03/03</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
+          <t>2020/11/08</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15693,12 +15693,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>1998-05-25</t>
+          <t>1998/05/25</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022/10/26</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>2023-06-08</t>
+          <t>2023/06/08</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15768,12 +15768,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>1977-10-14</t>
+          <t>1977/10/14</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2020-06-24</t>
+          <t>2020/06/24</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>2021-07-19</t>
+          <t>2021/07/19</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>1985-01-14</t>
+          <t>1985/01/14</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2018-06-21</t>
+          <t>2018/06/21</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -15910,12 +15910,12 @@
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>1975-03-05</t>
+          <t>1975/03/05</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018/02/26</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024/03/26</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15985,12 +15985,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2003-12-14</t>
+          <t>2003/12/14</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2023-11-06</t>
+          <t>2023/11/06</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16056,12 +16056,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>1991-02-19</t>
+          <t>1991/02/19</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2020/02/05</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16127,12 +16127,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>1995-05-05</t>
+          <t>1995/05/05</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2021-02-05</t>
+          <t>2021/02/05</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025/07/16</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16202,12 +16202,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2001-04-02</t>
+          <t>2001/04/02</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020/10/22</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16273,12 +16273,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>1990-04-10</t>
+          <t>1990/04/10</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
+          <t>2023/04/29</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>1986-10-16</t>
+          <t>1986/10/16</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2020-06-25</t>
+          <t>2020/06/25</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16382,7 +16382,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2027-06-16</t>
+          <t>2027/06/16</t>
         </is>
       </c>
       <c r="N222" t="inlineStr"/>
@@ -16415,12 +16415,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>1991-02-24</t>
+          <t>1991/02/24</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2019-02-24</t>
+          <t>2019/02/24</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2022-01-19</t>
+          <t>2022/01/19</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>1981-02-21</t>
+          <t>1981/02/21</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>2015-03-17</t>
+          <t>2015/03/17</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16551,12 +16551,12 @@
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2003-11-08</t>
+          <t>2003/11/08</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>2015-04-14</t>
+          <t>2015/04/14</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16589,7 +16589,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>2021-06-13</t>
+          <t>2021/06/13</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16626,12 +16626,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>1988-02-17</t>
+          <t>1988/02/17</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2015-03-13</t>
+          <t>2015/03/13</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16697,12 +16697,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>1989-02-11</t>
+          <t>1989/02/11</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2018-06-06</t>
+          <t>2018/06/06</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -16735,7 +16735,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2023/09/12</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16772,12 +16772,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>1976-07-28</t>
+          <t>1976/07/28</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>2019-11-02</t>
+          <t>2019/11/02</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -16843,12 +16843,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2003-04-18</t>
+          <t>2003/04/18</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>2019-01-14</t>
+          <t>2019/01/14</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
+          <t>2020/11/11</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16918,12 +16918,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>1991-07-25</t>
+          <t>1991/07/25</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2018/05/10</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021/03/17</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16993,12 +16993,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>1994-09-09</t>
+          <t>1994/09/09</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2017-08-27</t>
+          <t>2017/08/27</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17064,12 +17064,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>1984-01-20</t>
+          <t>1984/01/20</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2017-08-19</t>
+          <t>2017/08/19</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17102,7 +17102,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>2016-08-24</t>
+          <t>2016/08/24</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17139,12 +17139,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>1986-01-14</t>
+          <t>1986/01/14</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2015-04-25</t>
+          <t>2015/04/25</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17210,12 +17210,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>1978-11-05</t>
+          <t>1978/11/05</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2017-01-09</t>
+          <t>2017/01/09</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17279,12 +17279,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>1979-07-20</t>
+          <t>1979/07/20</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2016/06/06</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17351,7 +17351,7 @@
       <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2023/05/11</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17417,12 +17417,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2000-06-28</t>
+          <t>2000/06/28</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2016-02-24</t>
+          <t>2016/02/24</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17488,12 +17488,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>1980-03-18</t>
+          <t>1980/03/18</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2015-03-29</t>
+          <t>2015/03/29</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>2017-01-09</t>
+          <t>2017/01/09</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17563,12 +17563,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>1997-07-03</t>
+          <t>1997/07/03</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2017-06-21</t>
+          <t>2017/06/21</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2023/05/17</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17638,12 +17638,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>1993-08-15</t>
+          <t>1993/08/15</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>2019-12-30</t>
+          <t>2019/12/30</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17709,12 +17709,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>1990-11-18</t>
+          <t>1990/11/18</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>2021/07/10</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -17747,7 +17747,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>2021-03-17</t>
+          <t>2021/03/17</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17784,12 +17784,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>1983-10-22</t>
+          <t>1983/10/22</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>2019-04-06</t>
+          <t>2019/04/06</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -17822,7 +17822,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2018/07/01</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17859,12 +17859,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>1983-03-16</t>
+          <t>1983/03/16</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>2019-03-20</t>
+          <t>2019/03/20</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -17930,12 +17930,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>1980-04-20</t>
+          <t>1980/04/20</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>2016-11-08</t>
+          <t>2016/11/08</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18001,12 +18001,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2002-12-04</t>
+          <t>2002/12/04</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>2017-09-10</t>
+          <t>2017/09/10</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021/12/08</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18076,12 +18076,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>1999-11-21</t>
+          <t>1999/11/21</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>2019-08-27</t>
+          <t>2019/08/27</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18143,12 +18143,12 @@
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>1990-09-10</t>
+          <t>1990/09/10</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>2017-10-01</t>
+          <t>2017/10/01</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18181,7 +18181,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>2024/02/22</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18218,12 +18218,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>1977-09-22</t>
+          <t>1977/09/22</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2020-03-28</t>
+          <t>2020/03/28</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18287,12 +18287,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>1988-02-08</t>
+          <t>1988/02/08</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>2021-01-03</t>
+          <t>2021/01/03</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>2023-12-18</t>
+          <t>2023/12/18</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18362,12 +18362,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>1986-03-10</t>
+          <t>1986/03/10</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2022/05/04</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18433,12 +18433,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>1988-02-02</t>
+          <t>1988/02/02</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2024/12/04</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>2029-06-21</t>
+          <t>2029/06/21</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18508,12 +18508,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>1984-07-02</t>
+          <t>1984/07/02</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024/04/20</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18546,7 +18546,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>2030-07-28</t>
+          <t>2030/07/28</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18583,12 +18583,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>1982-12-11</t>
+          <t>1982/12/11</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2020/09/10</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18654,12 +18654,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>1988-06-13</t>
+          <t>1988/06/13</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2019-06-03</t>
+          <t>2019/06/03</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -18692,7 +18692,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024/07/06</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18729,12 +18729,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>1998-07-11</t>
+          <t>1998/07/11</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2016-08-15</t>
+          <t>2016/08/15</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>2017-12-13</t>
+          <t>2017/12/13</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2001-06-14</t>
+          <t>2001/06/14</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2017-11-10</t>
+          <t>2017/11/10</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -18867,12 +18867,12 @@
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>1994-10-27</t>
+          <t>1994/10/27</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2025/01/12</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2029-07-12</t>
+          <t>2029/07/12</t>
         </is>
       </c>
       <c r="N257" t="inlineStr"/>
@@ -18938,12 +18938,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>1990-04-11</t>
+          <t>1990/04/11</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2020-01-06</t>
+          <t>2020/01/06</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -18976,7 +18976,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>2021-06-18</t>
+          <t>2021/06/18</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19014,7 +19014,7 @@
       <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025/01/18</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024/04/24</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>1989-09-09</t>
+          <t>1989/09/09</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>2017-11-22</t>
+          <t>2017/11/22</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025/09/30</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19159,12 +19159,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>1998-09-04</t>
+          <t>1998/09/04</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024/09/06</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19226,12 +19226,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>1997-02-24</t>
+          <t>1997/02/24</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2022-09-25</t>
+          <t>2022/09/25</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19297,12 +19297,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>1989-09-08</t>
+          <t>1989/09/08</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022/05/07</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19335,7 +19335,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025/06/30</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19372,12 +19372,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>1983-08-06</t>
+          <t>1983/08/06</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2015-10-28</t>
+          <t>2015/10/28</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19410,7 +19410,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023/08/22</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19447,12 +19447,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>1998-09-03</t>
+          <t>1998/09/03</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2023-01-21</t>
+          <t>2023/01/21</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19518,12 +19518,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>1976-02-19</t>
+          <t>1976/02/19</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>2022-04-05</t>
+          <t>2022/04/05</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026/12/12</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19593,12 +19593,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2000-02-18</t>
+          <t>2000/02/18</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2017-08-03</t>
+          <t>2017/08/03</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2018-02-26</t>
+          <t>2018/02/26</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19668,12 +19668,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>1982-07-26</t>
+          <t>1982/07/26</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2017-11-10</t>
+          <t>2017/11/10</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>2017-05-29</t>
+          <t>2017/05/29</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19743,12 +19743,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>1999-03-15</t>
+          <t>1999/03/15</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>2015-10-23</t>
+          <t>2015/10/23</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -19814,12 +19814,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>1995-01-24</t>
+          <t>1995/01/24</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>2017-07-19</t>
+          <t>2017/07/19</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -19885,12 +19885,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>1981-11-18</t>
+          <t>1981/11/18</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>2019-09-06</t>
+          <t>2019/09/06</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>2020-04-08</t>
+          <t>2020/04/08</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19960,12 +19960,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>1979-07-26</t>
+          <t>1979/07/26</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2023/03/21</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20031,12 +20031,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>1983-08-01</t>
+          <t>1983/08/01</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024/04/24</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>2031-08-12</t>
+          <t>2031/08/12</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20106,12 +20106,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>1979-11-20</t>
+          <t>1979/11/20</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2022-08-18</t>
+          <t>2022/08/18</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20142,7 +20142,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023/07/26</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20179,12 +20179,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2015-05-05</t>
+          <t>2015/05/05</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024/02/24</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20217,7 +20217,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>2030-04-19</t>
+          <t>2030/04/19</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20254,12 +20254,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>1985-11-25</t>
+          <t>1985/11/25</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022/11/01</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20325,12 +20325,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>1981-04-25</t>
+          <t>1981/04/25</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>2017-10-14</t>
+          <t>2017/10/14</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
